--- a/ru/downloads/data-excel/6.a.1.1.xlsx
+++ b/ru/downloads/data-excel/6.a.1.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356C2487-04CA-4AAD-9174-267BB7321511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3375" yWindow="3375" windowWidth="15375" windowHeight="7875"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -86,7 +87,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;??_р_._-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _р_._-;\-* #,##0.00\ _р_._-;_-* &quot;-&quot;??\ _р_._-;_-@_-"/>
@@ -238,7 +239,7 @@
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -250,11 +251,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -267,27 +265,33 @@
     <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 10" xfId="3"/>
-    <cellStyle name="Обычный 2" xfId="4"/>
-    <cellStyle name="Обычный 2 2" xfId="5"/>
-    <cellStyle name="Обычный 2 3" xfId="6"/>
-    <cellStyle name="Обычный 3" xfId="7"/>
-    <cellStyle name="Обычный 3 2" xfId="8"/>
-    <cellStyle name="Обычный 4" xfId="9"/>
-    <cellStyle name="Обычный 5" xfId="10"/>
-    <cellStyle name="Обычный 6" xfId="2"/>
-    <cellStyle name="Обычный 7" xfId="1"/>
-    <cellStyle name="Обычный 8" xfId="11"/>
-    <cellStyle name="Обычный 9" xfId="12"/>
-    <cellStyle name="Пояснение 2" xfId="13"/>
-    <cellStyle name="Процентный 2" xfId="14"/>
-    <cellStyle name="Процентный 3" xfId="15"/>
-    <cellStyle name="Стиль 1" xfId="16"/>
-    <cellStyle name="Финансовый 2" xfId="17"/>
-    <cellStyle name="Финансовый 3" xfId="18"/>
+    <cellStyle name="Обычный 10" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 2 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Обычный 3" xfId="7" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Обычный 3 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Обычный 4" xfId="9" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Обычный 5" xfId="10" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Обычный 6" xfId="2" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Обычный 7" xfId="1" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Обычный 8" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Обычный 9" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Пояснение 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Процентный 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Процентный 3" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Стиль 1" xfId="16" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Финансовый 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Финансовый 3" xfId="18" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -564,8 +568,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AB17"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="3" width="36.7109375" style="1" customWidth="1"/>
@@ -573,7 +577,7 @@
     <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="78" customHeight="1">
+    <row r="1" spans="1:28" ht="78" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -584,7 +588,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:28">
       <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
@@ -595,8 +599,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="12.75" thickBot="1"/>
-    <row r="4" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
+    <row r="3" spans="1:28" ht="12.75" thickBot="1"/>
+    <row r="4" spans="1:28" ht="16.5" customHeight="1" thickBot="1">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -642,44 +646,47 @@
       <c r="O4" s="6">
         <v>2011</v>
       </c>
-      <c r="P4" s="7">
+      <c r="P4" s="6">
         <v>2012</v>
       </c>
-      <c r="Q4" s="7">
+      <c r="Q4" s="6">
         <v>2013</v>
       </c>
-      <c r="R4" s="7">
+      <c r="R4" s="6">
         <v>2014</v>
       </c>
       <c r="S4" s="6">
         <v>2015</v>
       </c>
-      <c r="T4" s="7">
+      <c r="T4" s="6">
         <v>2016</v>
       </c>
-      <c r="U4" s="7">
+      <c r="U4" s="6">
         <v>2017</v>
       </c>
-      <c r="V4" s="7">
+      <c r="V4" s="6">
         <v>2018</v>
       </c>
-      <c r="W4" s="7">
+      <c r="W4" s="6">
         <v>2019</v>
       </c>
-      <c r="X4" s="7">
+      <c r="X4" s="6">
         <v>2020</v>
       </c>
-      <c r="Y4" s="7">
+      <c r="Y4" s="6">
         <v>2021</v>
       </c>
-      <c r="Z4" s="7">
+      <c r="Z4" s="6">
         <v>2022</v>
       </c>
-      <c r="AA4" s="7">
+      <c r="AA4" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:27" ht="16.5" customHeight="1">
+      <c r="AB4" s="6">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" ht="16.5" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -689,80 +696,83 @@
       <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <v>36000</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="10">
+      <c r="E5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="9">
         <v>15000</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="M5" s="10">
+      <c r="G5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M5" s="9">
         <v>7150</v>
       </c>
-      <c r="N5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="O5" s="10">
+      <c r="N5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="O5" s="9">
         <v>7200</v>
       </c>
-      <c r="P5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q5" s="10">
+      <c r="P5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q5" s="9">
         <v>1950</v>
       </c>
-      <c r="R5" s="10">
+      <c r="R5" s="9">
         <v>10400</v>
       </c>
-      <c r="S5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="T5" s="10">
+      <c r="S5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="T5" s="9">
         <v>46950</v>
       </c>
-      <c r="U5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="V5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="W5" s="10">
+      <c r="U5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="V5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="W5" s="9">
         <v>50000</v>
       </c>
-      <c r="X5" s="10">
+      <c r="X5" s="9">
         <v>23780</v>
       </c>
-      <c r="Y5" s="10">
+      <c r="Y5" s="9">
         <v>44660</v>
       </c>
-      <c r="Z5" s="10">
+      <c r="Z5" s="9">
         <v>25000</v>
       </c>
-      <c r="AA5" s="10">
+      <c r="AA5" s="9">
         <v>13010</v>
       </c>
-    </row>
-    <row r="6" spans="1:27" ht="16.5" customHeight="1">
+      <c r="AB5" s="11">
+        <v>38818.94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="16.5" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -772,372 +782,378 @@
       <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="I6" s="10">
+      <c r="D6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="9">
         <v>7200</v>
       </c>
-      <c r="J6" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="L6" s="10">
+      <c r="J6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6" s="9">
         <v>8700</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="9">
         <v>6500</v>
       </c>
-      <c r="N6" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="O6" s="10">
+      <c r="N6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="O6" s="9">
         <v>13860</v>
       </c>
-      <c r="P6" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q6" s="10">
+      <c r="P6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q6" s="9">
         <v>7350</v>
       </c>
-      <c r="R6" s="10">
+      <c r="R6" s="9">
         <v>11185</v>
       </c>
-      <c r="S6" s="10">
+      <c r="S6" s="9">
         <v>5772.3</v>
       </c>
-      <c r="T6" s="10">
+      <c r="T6" s="9">
         <v>12402.5</v>
       </c>
-      <c r="U6" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="V6" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="W6" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="X6" s="10">
+      <c r="U6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="V6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="W6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="X6" s="9">
         <v>38240</v>
       </c>
-      <c r="Y6" s="10">
+      <c r="Y6" s="9">
         <v>7950</v>
       </c>
-      <c r="Z6" s="10">
+      <c r="Z6" s="9">
         <v>23000</v>
       </c>
-      <c r="AA6" s="10">
+      <c r="AA6" s="9">
         <v>16390</v>
       </c>
-    </row>
-    <row r="7" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A7" s="9" t="s">
+      <c r="AB6" s="11">
+        <v>34524.160000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" ht="16.5" customHeight="1" thickBot="1">
+      <c r="A7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="M7" s="11">
+      <c r="D7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="M7" s="10">
         <v>10000</v>
       </c>
-      <c r="N7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="O7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="P7" s="11">
+      <c r="N7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="P7" s="10">
         <v>7000</v>
       </c>
-      <c r="Q7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="R7" s="11">
+      <c r="Q7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="R7" s="10">
         <v>4890</v>
       </c>
-      <c r="S7" s="11">
+      <c r="S7" s="10">
         <v>9100</v>
       </c>
-      <c r="T7" s="11">
+      <c r="T7" s="10">
         <v>30100</v>
       </c>
-      <c r="U7" s="11">
+      <c r="U7" s="10">
         <v>59930</v>
       </c>
-      <c r="V7" s="11">
+      <c r="V7" s="10">
         <v>48020</v>
       </c>
-      <c r="W7" s="11">
+      <c r="W7" s="10">
         <v>24887.5</v>
       </c>
-      <c r="X7" s="11">
+      <c r="X7" s="10">
         <v>62020</v>
       </c>
-      <c r="Y7" s="11">
+      <c r="Y7" s="10">
         <v>52610</v>
       </c>
-      <c r="Z7" s="11">
+      <c r="Z7" s="10">
         <v>48000</v>
       </c>
-      <c r="AA7" s="11">
+      <c r="AA7" s="10">
         <v>29400</v>
       </c>
-    </row>
-    <row r="8" spans="1:27">
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-    </row>
-    <row r="9" spans="1:27">
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-    </row>
-    <row r="10" spans="1:27">
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="8"/>
-    </row>
-    <row r="11" spans="1:27">
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="8"/>
-    </row>
-    <row r="12" spans="1:27">
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="8"/>
-    </row>
-    <row r="13" spans="1:27">
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="8"/>
-    </row>
-    <row r="14" spans="1:27">
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
-      <c r="T14" s="8"/>
-      <c r="U14" s="8"/>
-      <c r="V14" s="8"/>
-    </row>
-    <row r="15" spans="1:27">
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="8"/>
-      <c r="U15" s="8"/>
-      <c r="V15" s="8"/>
-    </row>
-    <row r="16" spans="1:27">
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
+      <c r="AB7" s="12">
+        <v>73343.100000000006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+    </row>
+    <row r="9" spans="1:28">
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+    </row>
+    <row r="10" spans="1:28">
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+    </row>
+    <row r="11" spans="1:28">
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+    </row>
+    <row r="12" spans="1:28">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+    </row>
+    <row r="13" spans="1:28">
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+    </row>
+    <row r="14" spans="1:28">
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+    </row>
+    <row r="15" spans="1:28">
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+    </row>
+    <row r="16" spans="1:28">
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
     </row>
     <row r="17" spans="4:22">
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
